--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -82,58 +82,151 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
     <t>GUILLEN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>LINARES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
   </si>
   <si>
     <t>CINTHIA</t>
@@ -142,25 +235,22 @@
     <t>MARLENE ALICIA</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
     <t>EDITH</t>
   </si>
   <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
     <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
   </si>
   <si>
     <t>JANETH</t>
@@ -1088,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,232 +1210,485 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920163</v>
+        <v>19330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920140</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920195</v>
+        <v>19330051920095</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920202</v>
+        <v>19330051920099</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330061460390</v>
+        <v>19330051920118</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920038</v>
+        <v>19330051920119</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920276</v>
+        <v>19330051920207</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920102</v>
+        <v>19330051920016</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920197</v>
+        <v>19330051920022</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920213</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920038</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920276</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920163</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920140</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920122</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920195</v>
+      </c>
+      <c r="B19" t="s">
         <v>38</v>
       </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G11">
-        <v>6</v>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920197</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920202</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920213</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -97,102 +97,45 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ROMAN</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>IVAN</t>
   </si>
   <si>
@@ -208,52 +151,16 @@
     <t>ROMARIO ALDAIR</t>
   </si>
   <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
     <t>JESSICA</t>
   </si>
   <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
     <t>NATANAEL</t>
   </si>
   <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
     <t>MARLENE ALICIA</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
     <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>JANETH</t>
   </si>
 </sst>
 </file>
@@ -654,19 +561,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -680,19 +587,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -732,19 +639,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -758,19 +665,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -784,19 +691,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -849,16 +756,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>63.16</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -872,16 +782,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>29</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.86</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -895,16 +808,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.91</v>
+      </c>
+      <c r="H4">
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -918,16 +834,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <v>16</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -941,16 +860,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H6">
+        <v>9.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -964,16 +886,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H7">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -1026,19 +951,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1052,19 +977,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1090,7 +1015,7 @@
         <v>91.3</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1104,16 +1029,16 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H5">
         <v>8.800000000000001</v>
@@ -1130,19 +1055,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1156,16 +1081,16 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -1178,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1216,10 +1141,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1239,10 +1164,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1262,10 +1187,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1285,10 +1210,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1308,10 +1233,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1325,369 +1250,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920119</v>
+        <v>19330051920016</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920207</v>
+        <v>18330061460390</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920016</v>
+        <v>19330051920140</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920022</v>
+        <v>19330051920116</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>18330061460390</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920038</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920163</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920140</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920116</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920122</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920195</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920197</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920202</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920213</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
@@ -94,7 +97,7 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>ENCARNACION</t>
@@ -103,15 +106,12 @@
     <t>ROMAN</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -121,7 +121,7 @@
     <t>DIAZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ANGUIANO</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -130,15 +130,12 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>IVAN</t>
   </si>
   <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
     <t>ELEAZAR RIGOBERTO</t>
   </si>
   <si>
@@ -148,19 +145,13 @@
     <t>ADRIANA</t>
   </si>
   <si>
-    <t>ROMARIO ALDAIR</t>
+    <t>JOSUE</t>
   </si>
   <si>
     <t>JESSICA</t>
   </si>
   <si>
     <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1141,10 +1132,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,22 +1149,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920092</v>
+        <v>19330051920140</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1181,16 +1172,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920095</v>
+        <v>19330051920092</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1204,16 +1195,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920099</v>
+        <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1222,21 +1213,21 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920118</v>
+        <v>19330051920099</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1250,39 +1241,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920016</v>
+        <v>19330051920116</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330061460390</v>
+        <v>19330051920016</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1296,48 +1287,25 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920140</v>
+        <v>18330061460390</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,78 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
   </si>
 </sst>
 </file>
@@ -552,19 +480,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>73.68000000000001</v>
+        <v>97.37</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -578,19 +506,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -604,19 +532,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -630,19 +558,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>59.38</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -656,19 +584,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -682,19 +610,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -747,19 +675,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>63.16</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -773,19 +701,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,19 +727,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>73.91</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -825,19 +753,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -851,19 +779,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -877,19 +805,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>60.61</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -942,19 +870,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -968,19 +896,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -994,19 +922,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,19 +948,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>59.38</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1046,16 +974,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>9.300000000000001</v>
@@ -1072,19 +1000,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1094,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1124,190 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920040</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920140</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920092</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920095</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920099</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920116</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920016</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>18330061460390</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
